--- a/data/trans_orig/P6903-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6903-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49760</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>57574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86776</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81442</t>
+          <t>81092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104527</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49431</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65112</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134790</t>
+          <t>135309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163879</t>
+          <t>163992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57134</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82984</t>
+          <t>80792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55419</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113086</t>
+          <t>115278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139916</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71040</t>
+          <t>70726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>90341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27897</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92315</t>
+          <t>92415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114987</t>
+          <t>115156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>42102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>40926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242444</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301759</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>342692</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164884</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>449983</t>
+          <t>449530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>500203</t>
+          <t>500323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31776</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35499</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59939</t>
+          <t>59900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>52673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70320</t>
+          <t>70481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>33597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92419</t>
+          <t>92458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116859</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67183</t>
+          <t>68048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60572</t>
+          <t>61193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78303</t>
+          <t>78975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36716</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103324</t>
+          <t>102459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128358</t>
+          <t>128046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63613</t>
+          <t>63533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78681</t>
+          <t>78662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91050</t>
+          <t>91302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>111058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31377</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132031</t>
+          <t>129351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>175264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231652</t>
+          <t>230438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>261995</t>
+          <t>261024</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>125651</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153571</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>364599</t>
+          <t>363717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>406950</t>
+          <t>409630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39915</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>34641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56685</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59998</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36651</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71178</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91966</t>
+          <t>93222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>52214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39489</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>60430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87411</t>
+          <t>87109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>60909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81038</t>
+          <t>81652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97170</t>
+          <t>97472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124319</t>
+          <t>124151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46687</t>
+          <t>46358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30391</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>48042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>72779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73376</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99146</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117870</t>
+          <t>117715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>156230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202214</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>250839</t>
+          <t>251475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>195142</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232131</t>
+          <t>232286</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315460</t>
+          <t>314824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>364085</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58970</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>43825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36337</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>74898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36510</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66373</t>
+          <t>67759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>59250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77239</t>
+          <t>77059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>53621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104711</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127154</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49944</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118316</t>
+          <t>116658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>57364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>77117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77734</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129507</t>
+          <t>127056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142714</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>199079</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>38190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56016</t>
+          <t>56502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>36654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50852</t>
+          <t>50876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66068</t>
+          <t>65582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>83894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -11385,97 +11385,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>34,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>80,91%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>993</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2415</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>34,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137275</t>
+          <t>133498</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>101182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160985</t>
+          <t>160700</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>214441</t>
+          <t>209245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>199580</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240217</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>192834</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253535</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>407483</t>
+          <t>408087</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>475948</t>
+          <t>481144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
